--- a/data/trans_orig/IP1008-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Estudios-trans_orig.xlsx
@@ -737,7 +737,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4571</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -752,7 +752,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4967</t>
+          <t>4712</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -787,7 +787,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>5,43%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>660</t>
+          <t>673</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6041</t>
+          <t>6477</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,64%</t>
         </is>
       </c>
     </row>
@@ -845,7 +845,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>86296</t>
+          <t>86944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,97%</t>
+          <t>95,68%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -880,7 +880,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81878</t>
+          <t>82133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -895,7 +895,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171671</t>
+          <t>171235</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177052</t>
+          <t>177039</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,36%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
     </row>
@@ -1080,7 +1080,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5699</t>
+          <t>4908</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1095,7 +1095,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1115,7 +1115,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5530</t>
+          <t>4480</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1130,7 +1130,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>706</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6910</t>
+          <t>6941</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
     </row>
@@ -1188,7 +1188,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>410388</t>
+          <t>411179</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,63%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -1223,7 +1223,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>471461</t>
+          <t>472511</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886168</t>
+          <t>886137</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892372</t>
+          <t>892371</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>2660</t>
+          <t>2218</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1438,7 +1438,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4763</t>
+          <t>4115</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>526</t>
+          <t>525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5270</t>
+          <t>5048</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,52%</t>
         </is>
       </c>
     </row>
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>171406</t>
+          <t>171848</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,73%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1566,7 +1566,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>153375</t>
+          <t>154023</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>326935</t>
+          <t>327157</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331679</t>
+          <t>331680</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,41%</t>
+          <t>98,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1184</t>
+          <t>1183</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7671</t>
+          <t>7365</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>1386</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>8878</t>
+          <t>9387</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,47 +1811,47 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>1,3%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>7321</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>3970</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>12494</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
           <t>0,28%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>7321</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>3968</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>12917</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V13" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>673350</t>
+          <t>673656</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>679837</t>
+          <t>679838</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>713096</t>
+          <t>712587</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>719951</t>
+          <t>720588</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1390078</t>
+          <t>1390501</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399027</t>
+          <t>1399025</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,7 +1959,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -2375,7 +2375,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4595</t>
+          <t>4285</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2390,7 +2390,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,13%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2410,7 +2410,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4553</t>
+          <t>4573</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2425,7 +2425,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>78942</t>
+          <t>79252</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>94,5%</t>
+          <t>94,87%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170872</t>
+          <t>170852</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2533,7 +2533,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,4%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>629</t>
+          <t>628</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>5919</t>
+          <t>6132</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2698,7 +2698,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>607</t>
+          <t>608</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5332</t>
+          <t>5953</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2733,7 +2733,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1921</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>9048</t>
+          <t>8167</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2763,12 +2763,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,2%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,87%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>443781</t>
+          <t>443568</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>449071</t>
+          <t>449072</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>487072</t>
+          <t>486451</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>491797</t>
+          <t>491796</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933055</t>
+          <t>933936</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>940696</t>
+          <t>940182</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,13%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,85%</t>
+          <t>99,8%</t>
         </is>
       </c>
     </row>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>4921</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3096,7 +3096,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>159689</t>
+          <t>160419</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3149,7 +3149,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>331966</t>
+          <t>332356</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3364,12 +3364,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1355</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7909</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3384,7 +3384,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3399,12 +3399,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>1266</t>
+          <t>1249</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6645</t>
+          <t>7664</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3419,7 +3419,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3536</t>
+          <t>3362</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12857</t>
+          <t>12011</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3449,12 +3449,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3477,12 +3477,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>699019</t>
+          <t>698695</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>705573</t>
+          <t>705570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,84%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -3512,12 +3512,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>740856</t>
+          <t>739837</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>746235</t>
+          <t>746252</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3527,7 +3527,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1441572</t>
+          <t>1442418</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1450893</t>
+          <t>1451067</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,12 +3562,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,17%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,76%</t>
+          <t>99,77%</t>
         </is>
       </c>
     </row>
@@ -3943,7 +3943,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5063</t>
+          <t>5056</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>8,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4013,7 +4013,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>5869</t>
+          <t>4949</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4028,7 +4028,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>3,87%</t>
         </is>
       </c>
     </row>
@@ -4051,7 +4051,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>54315</t>
+          <t>54322</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -4066,7 +4066,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,47%</t>
+          <t>91,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>122124</t>
+          <t>123044</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>96,13%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4281,12 +4281,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1300</t>
+          <t>1350</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>7680</t>
+          <t>8175</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4296,12 +4296,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4321,7 +4321,7 @@
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>3348</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1374</t>
+          <t>1398</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>8590</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4366,12 +4366,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -4394,12 +4394,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>464610</t>
+          <t>464115</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>470990</t>
+          <t>470940</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4409,12 +4409,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4429,7 +4429,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>485387</t>
+          <t>486056</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,31%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952907</t>
+          <t>952435</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959651</t>
+          <t>959627</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,12 +4479,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,11%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,86%</t>
+          <t>99,85%</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4629,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4731</t>
+          <t>4426</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4644,7 +4644,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4664,7 +4664,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4831</t>
+          <t>4836</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4694,12 +4694,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>639</t>
+          <t>641</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>6073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,69%</t>
         </is>
       </c>
     </row>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>167972</t>
+          <t>168277</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -4752,7 +4752,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,26%</t>
+          <t>97,44%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>182664</t>
+          <t>182659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>353846</t>
+          <t>354124</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>359558</t>
+          <t>359556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4967,12 +4967,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2847</t>
+          <t>2826</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11565</t>
+          <t>11751</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4987,7 +4987,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,67%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5002,12 +5002,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>584</t>
+          <t>587</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>5077</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5022,7 +5022,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4688</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13915</t>
+          <t>13786</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5052,12 +5052,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -5080,12 +5080,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>692806</t>
+          <t>692620</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>701524</t>
+          <t>701545</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5095,7 +5095,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -5115,12 +5115,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>739767</t>
+          <t>739423</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744260</t>
+          <t>744257</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5130,7 +5130,7 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>99,32%</t>
+          <t>99,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1435300</t>
+          <t>1435429</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1444527</t>
+          <t>1445006</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,12 +5165,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,04%</t>
+          <t>99,05%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,68%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/IP1008-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/IP1008-Estudios-trans_orig.xlsx
@@ -543,7 +543,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -554,7 +554,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -727,67 +727,67 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
+          <t>1353</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4659</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,56%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,37%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>1296</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>1,43%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>4,32%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>1353</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4712</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,56%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>5,43%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>673</t>
+          <t>670</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6477</t>
+          <t>6549</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,69%</t>
         </is>
       </c>
     </row>
@@ -835,74 +835,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>85492</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>82186</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,44%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,63%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>134</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>89571</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>86944</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>86778</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>98,57%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>95,68%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>95,5%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>128</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>85492</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>82133</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,44%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,57%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>262</t>
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>171235</t>
+          <t>171163</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>177039</t>
+          <t>177042</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,31%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -948,57 +948,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>86845</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>136</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>90867</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>130</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>86845</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1070,67 +1070,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1390</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>4852</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,29%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,02%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>1398</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>4908</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,34%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1390</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>4480</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,94%</t>
+          <t>1,27%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>707</t>
+          <t>685</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>6941</t>
+          <t>6356</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,71%</t>
         </is>
       </c>
     </row>
@@ -1178,74 +1178,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>475601</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>472139</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,71%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,98%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>626</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>414689</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>411179</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>410799</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,66%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,82%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,73%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>717</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>475601</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>472511</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>99,06%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1343</t>
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>886137</t>
+          <t>886722</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892371</t>
+          <t>892393</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1291,57 +1291,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>719</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>476991</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>628</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>416087</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>719</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>476991</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1408,72 +1408,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1358</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,86%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>527</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>2218</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2664</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,3%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>1,27%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4115</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,86%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>2,6%</t>
+          <t>1,53%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>525</t>
+          <t>527</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>5048</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1508,7 +1508,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,61%</t>
         </is>
       </c>
     </row>
@@ -1521,74 +1521,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>234</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>156780</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>153389</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,14%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,0%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>253</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>173539</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>171848</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>171402</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,7%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>98,73%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>98,47%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>234</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>156780</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>154023</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>99,14%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>487</t>
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>327157</t>
+          <t>326856</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>331680</t>
+          <t>331678</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,48%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1634,57 +1634,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>236</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>158138</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>254</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>174066</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>236</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>158138</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1751,72 +1751,72 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>4101</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1785</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>8224</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,57%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,25%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>1,14%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>3220</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1183</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>7365</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1167</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>7780</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,47%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,17%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,08%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>4101</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1386</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>9387</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,57%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3970</t>
+          <t>3999</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12494</t>
+          <t>12735</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -1864,74 +1864,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1079</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>717873</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>713750</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>720189</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,43%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,75%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>677801</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>673656</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>679838</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>673241</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>679854</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,53%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,92%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,86%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,83%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1079</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>717873</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>712587</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>720588</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,43%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,81%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2092</t>
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1390501</t>
+          <t>1390260</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1399025</t>
+          <t>1398996</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,72%</t>
+          <t>99,71%</t>
         </is>
       </c>
     </row>
@@ -1977,57 +1977,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1085</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>721974</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>681021</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1085</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>721974</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2146,7 +2146,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -2157,7 +2157,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -2325,92 +2325,92 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>4749</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>1,55%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>5,68%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="Q4" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="R4" s="2" t="inlineStr">
         <is>
           <t>1299</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>4285</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>1,55%</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>5,13%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1299</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>4573</t>
+          <t>4580</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2438,74 +2438,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>82238</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>78788</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>98,45%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>94,32%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>115</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>82238</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>79252</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>98,45%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>94,87%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>248</t>
@@ -2518,7 +2518,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>170852</t>
+          <t>170845</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -2551,57 +2551,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>83537</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>133</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>91889</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>117</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>83537</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -2673,67 +2673,67 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
+          <t>1968</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>607</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>5288</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>1,07%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
           <t>2055</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>628</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>6132</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>626</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>5590</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,46%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="O7" s="2" t="inlineStr">
         <is>
           <t>0,14%</t>
         </is>
       </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>1968</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>608</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>5953</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2753,7 +2753,7 @@
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8167</t>
+          <t>8892</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2768,7 +2768,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -2781,74 +2781,74 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>490436</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>487116</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>491797</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,6%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>98,93%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>648</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>447645</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>443568</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>449072</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>444110</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>449074</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,54%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,64%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>98,76%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>99,86%</t>
         </is>
       </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>702</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>490436</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>486451</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>491796</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>98,79%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
       <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1350</t>
@@ -2861,7 +2861,7 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>933936</t>
+          <t>933211</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,13%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -2894,57 +2894,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>705</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>492404</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>651</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>449700</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>705</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>492404</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3011,107 +3011,107 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="K10" s="2" t="inlineStr">
         <is>
           <t>1442</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4921</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4766</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,87%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,98%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,88%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1442</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>5503</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1442</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4545</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,43%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,63%</t>
         </is>
       </c>
     </row>
@@ -3124,74 +3124,74 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>232</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>163898</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>160419</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>160574</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,13%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,02%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,12%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q11" s="2" t="inlineStr">
         <is>
           <t>475</t>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>332356</t>
+          <t>331398</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
@@ -3219,7 +3219,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -3237,57 +3237,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>243</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>171561</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>234</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>165340</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>243</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>171561</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -3359,67 +3359,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>3267</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>1219</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>7214</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,97%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
           <t>3498</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>1358</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>8233</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>1360</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>8640</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,49%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
         <is>
           <t>0,19%</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>1,16%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>3267</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>1249</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>7664</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,17%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3434,12 +3434,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3362</t>
+          <t>3398</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>12011</t>
+          <t>12265</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3454,7 +3454,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,84%</t>
         </is>
       </c>
     </row>
@@ -3467,74 +3467,74 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1060</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>744234</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>740287</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>746282</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,56%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,03%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,84%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1013</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>703430</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>698695</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>705570</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>698288</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>705568</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,51%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>98,84%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>98,78%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>99,81%</t>
         </is>
       </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1060</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>744234</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739837</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>746252</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,56%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>98,97%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>99,83%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>2073</t>
@@ -3547,12 +3547,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1442418</t>
+          <t>1442164</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1451067</t>
+          <t>1451031</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3562,7 +3562,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,17%</t>
+          <t>99,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -3580,57 +3580,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>747501</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1018</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>706928</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>747501</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -3749,7 +3749,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -3760,7 +3760,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -3928,107 +3928,107 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="K4" s="2" t="inlineStr">
         <is>
           <t>1579</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>5056</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>5370</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
         <is>
           <t>2,66%</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="O4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>8,51%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>9,04%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1579</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6342</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>1,23%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1579</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>4949</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>1,23%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>3,87%</t>
+          <t>4,96%</t>
         </is>
       </c>
     </row>
@@ -4041,74 +4041,74 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>87</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
         <is>
           <t>57799</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>54322</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>54008</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>97,34%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>91,49%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
+        <is>
+          <t>90,96%</t>
+        </is>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>—%</t>
-        </is>
-      </c>
       <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>186</t>
@@ -4121,7 +4121,7 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>123044</t>
+          <t>121651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
@@ -4136,7 +4136,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>96,13%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -4154,57 +4154,57 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>99</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>68614</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>89</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="K6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="L6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="M6" s="2" t="inlineStr">
         <is>
           <t>59378</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>99</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
-        </is>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>68614</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4271,72 +4271,72 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>2945</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="K7" s="2" t="inlineStr">
         <is>
           <t>3400</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>1350</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>8175</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>1299</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>8070</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
         <is>
           <t>0,72%</t>
         </is>
       </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>0,29%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>1,73%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>588</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>2679</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4351,12 +4351,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1398</t>
+          <t>1407</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>8590</t>
+          <t>8418</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -4384,72 +4384,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>694</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>488147</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>485790</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>99,88%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>99,4%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>709</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="K8" s="2" t="inlineStr">
         <is>
           <t>468890</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>464115</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>470940</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>464220</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>470991</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
         <is>
           <t>99,28%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>98,27%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>99,71%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>694</t>
-        </is>
-      </c>
-      <c r="K8" s="2" t="inlineStr">
-        <is>
-          <t>488147</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>486056</t>
-        </is>
-      </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>99,88%</t>
-        </is>
-      </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>98,29%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>100,0%</t>
+          <t>99,72%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4464,12 +4464,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>952435</t>
+          <t>952607</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>959627</t>
+          <t>959618</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4479,7 +4479,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>99,11%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -4497,57 +4497,57 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>695</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>488735</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>714</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="L9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
         <is>
           <t>472290</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>695</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>488735</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -4619,94 +4619,94 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
+          <t>1361</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>4867</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,73%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2,6%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
           <t>1255</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="L10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>4426</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4012</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>2,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>1361</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4836</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>2,32%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>2616</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
+          <t>639</t>
+        </is>
+      </c>
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>6065</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
         <is>
           <t>0,73%</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>2,58%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>2616</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>641</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>6073</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,18%</t>
@@ -4714,7 +4714,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,68%</t>
         </is>
       </c>
     </row>
@@ -4727,102 +4727,102 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>269</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>186134</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>182628</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>99,27%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>97,4%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100,0%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>256</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="K11" s="2" t="inlineStr">
         <is>
           <t>171448</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>168277</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>168691</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr">
+      <c r="N11" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>97,44%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>97,68%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
         <is>
           <t>100,0%</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>269</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>186134</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>182659</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>525</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>357581</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>354132</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>359558</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
         <is>
           <t>99,27%</t>
         </is>
       </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>97,42%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>100,0%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>525</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>357581</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>354124</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>359556</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -4840,57 +4840,57 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>271</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>187495</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>258</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="K12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="L12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="M12" s="2" t="inlineStr">
         <is>
           <t>172703</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>271</t>
-        </is>
-      </c>
-      <c r="K12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="L12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
-        </is>
-      </c>
-      <c r="M12" s="2" t="inlineStr">
-        <is>
-          <t>187495</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4957,74 +4957,74 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>1949</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>588</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5708</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>0,26%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>0,08%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0,77%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="K13" s="2" t="inlineStr">
         <is>
           <t>6235</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>2826</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>11751</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>2906</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>11767</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
         <is>
           <t>0,89%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="O13" s="2" t="inlineStr">
+        <is>
+          <t>0,41%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
         <is>
           <t>1,67%</t>
         </is>
       </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>1949</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>587</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>5421</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>0,26%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>0,08%</t>
-        </is>
-      </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>0,73%</t>
-        </is>
-      </c>
       <c r="Q13" s="2" t="inlineStr">
         <is>
           <t>12</t>
@@ -5037,12 +5037,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4209</t>
+          <t>4177</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13786</t>
+          <t>13601</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5057,7 +5057,7 @@
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>0,94%</t>
         </is>
       </c>
     </row>
@@ -5070,72 +5070,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1062</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>742895</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>739136</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>744256</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>99,74%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>99,23%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>99,92%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>1052</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="K14" s="2" t="inlineStr">
         <is>
           <t>698136</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>692620</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>701545</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>692604</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>701465</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
         <is>
           <t>99,11%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="O14" s="2" t="inlineStr">
         <is>
           <t>98,33%</t>
         </is>
       </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>99,6%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>1062</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>742895</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>739423</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>744257</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>99,74%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>99,27%</t>
-        </is>
-      </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>99,92%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5150,12 +5150,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1435429</t>
+          <t>1435614</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1445006</t>
+          <t>1445038</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5165,7 +5165,7 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>99,05%</t>
+          <t>99,06%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
@@ -5183,57 +5183,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>1065</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>744844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>1061</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="K15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="L15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr">
+      <c r="M15" s="2" t="inlineStr">
         <is>
           <t>704371</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>1065</t>
-        </is>
-      </c>
-      <c r="K15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="L15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
-        </is>
-      </c>
-      <c r="M15" s="2" t="inlineStr">
-        <is>
-          <t>744844</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
